--- a/TeplosilaWeb/Content/properties/gtrv3.xlsx
+++ b/TeplosilaWeb/Content/properties/gtrv3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pge27\OneDrive\Рабочий стол\TeploSilaWeb\TeplosilaWeb\Content\properties\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2368222-CA30-4E7F-9F10-3593D10AD610}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F5C12746-E548-47BA-B237-614272E24B09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-5025" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="42">
   <si>
     <t>Наименование параметров,
 единицы измерения</t>
@@ -70,15 +70,9 @@
     <t>TSL-3000-60-1-230-IP67</t>
   </si>
   <si>
-    <t>TSL-1600-25-1T-230-IP67</t>
-  </si>
-  <si>
     <t>TSL-1600-25-1TR-230-IP67</t>
   </si>
   <si>
-    <t>TSL-2200-40-1T-230-IP67</t>
-  </si>
-  <si>
     <t>TSL-2200-40-1TR-230-IP67</t>
   </si>
   <si>
@@ -140,13 +134,34 @@
   </si>
   <si>
     <t>TSL-3000-40-2AS-230-IP67</t>
+  </si>
+  <si>
+    <t>200*</t>
+  </si>
+  <si>
+    <t>TSL-1600-25-2T-230-IP67</t>
+  </si>
+  <si>
+    <t>TSL-2200-25-2AS-24-IP67</t>
+  </si>
+  <si>
+    <t>TSL-3000-40-1RS-230-IP67</t>
+  </si>
+  <si>
+    <t>TSL-2200-40-2T-230-IP67</t>
+  </si>
+  <si>
+    <t>TSL-3000-40-2AS-24-IP67</t>
+  </si>
+  <si>
+    <t>TSL-3000-60-2T-230-IP67</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -187,6 +202,45 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -196,7 +250,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -223,43 +277,6 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -296,28 +313,24 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -600,32 +613,34 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O63"/>
+  <dimension ref="A1:O71"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.85546875" customWidth="1"/>
     <col min="2" max="2" width="25.42578125" style="9" customWidth="1"/>
-    <col min="3" max="15" width="9.140625" style="9"/>
+    <col min="3" max="13" width="9.140625" style="9"/>
+    <col min="14" max="14" width="9.140625" style="11"/>
+    <col min="15" max="15" width="9.140625" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
-      <c r="J1" s="11"/>
-      <c r="K1" s="11"/>
-      <c r="L1" s="11"/>
-      <c r="M1" s="11"/>
-      <c r="N1" s="11"/>
-      <c r="O1"/>
+      <c r="A1" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
     </row>
     <row r="2" spans="1:15" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -634,7 +649,7 @@
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="16" t="s">
         <v>1</v>
       </c>
       <c r="D2" s="16"/>
@@ -648,7 +663,7 @@
       <c r="L2" s="16"/>
       <c r="M2" s="16"/>
       <c r="N2" s="16"/>
-      <c r="O2" s="17"/>
+      <c r="O2" s="16"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
@@ -693,8 +708,8 @@
       <c r="N3" s="4">
         <v>200</v>
       </c>
-      <c r="O3" s="4">
-        <v>201</v>
+      <c r="O3" s="4" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
@@ -737,10 +752,10 @@
       <c r="M4" s="7">
         <v>480</v>
       </c>
-      <c r="N4" s="7">
+      <c r="N4" s="5">
         <v>495</v>
       </c>
-      <c r="O4" s="7">
+      <c r="O4" s="5">
         <v>600</v>
       </c>
     </row>
@@ -784,10 +799,10 @@
       <c r="M5" s="7">
         <v>240</v>
       </c>
-      <c r="N5" s="7">
+      <c r="N5" s="5">
         <v>165</v>
       </c>
-      <c r="O5" s="7">
+      <c r="O5" s="5">
         <v>230</v>
       </c>
     </row>
@@ -795,22 +810,22 @@
       <c r="A6" s="2">
         <v>4</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="13"/>
-      <c r="L6" s="13"/>
-      <c r="M6" s="13"/>
-      <c r="N6" s="14"/>
-      <c r="O6"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="15"/>
+      <c r="L6" s="15"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="15"/>
+      <c r="O6" s="15"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
@@ -850,7 +865,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C8" s="7">
         <v>315</v>
@@ -916,7 +931,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C10" s="7">
         <v>315</v>
@@ -945,44 +960,44 @@
       <c r="O10" s="5"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="2">
+      <c r="A11" s="14">
         <v>9</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11" s="7">
+      <c r="B11" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="10">
         <v>315</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="10">
         <v>320</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="10">
         <v>325</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="10">
         <v>330</v>
       </c>
-      <c r="G11" s="7">
+      <c r="G11" s="10">
         <v>335</v>
       </c>
-      <c r="H11" s="7">
+      <c r="H11" s="10">
         <v>335</v>
       </c>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="5"/>
-      <c r="L11" s="5"/>
-      <c r="M11" s="5"/>
-      <c r="N11" s="5"/>
-      <c r="O11" s="5"/>
+      <c r="I11" s="10"/>
+      <c r="J11" s="10"/>
+      <c r="K11" s="10"/>
+      <c r="L11" s="10"/>
+      <c r="M11" s="10"/>
+      <c r="N11" s="10"/>
+      <c r="O11" s="10"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>10</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C12" s="7">
         <v>315</v>
@@ -1015,7 +1030,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C13" s="7">
         <v>315</v>
@@ -1048,7 +1063,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C14" s="7">
         <v>315</v>
@@ -1081,7 +1096,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C15" s="7">
         <v>315</v>
@@ -1114,7 +1129,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C16" s="7">
         <v>315</v>
@@ -1143,60 +1158,66 @@
       <c r="O16" s="5"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="2">
+      <c r="A17" s="14">
         <v>15</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C17" s="7">
+      <c r="B17" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" s="10">
         <v>315</v>
       </c>
-      <c r="D17" s="7">
+      <c r="D17" s="10">
         <v>320</v>
       </c>
-      <c r="E17" s="7">
+      <c r="E17" s="10">
         <v>325</v>
       </c>
-      <c r="F17" s="7">
+      <c r="F17" s="10">
         <v>330</v>
       </c>
-      <c r="G17" s="7">
+      <c r="G17" s="10">
         <v>335</v>
       </c>
-      <c r="H17" s="7">
+      <c r="H17" s="10">
         <v>335</v>
       </c>
-      <c r="I17" s="5"/>
-      <c r="J17" s="5"/>
-      <c r="K17" s="5"/>
-      <c r="L17" s="5"/>
-      <c r="M17" s="5"/>
-      <c r="N17" s="5"/>
-      <c r="O17" s="5"/>
+      <c r="I17" s="10"/>
+      <c r="J17" s="10"/>
+      <c r="K17" s="10"/>
+      <c r="L17" s="10"/>
+      <c r="M17" s="10"/>
+      <c r="N17" s="10"/>
+      <c r="O17" s="10"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>16</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
-      <c r="H18" s="5"/>
-      <c r="I18" s="7">
-        <v>445</v>
-      </c>
-      <c r="J18" s="7">
-        <v>445</v>
-      </c>
-      <c r="K18" s="7">
-        <v>480</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="C18" s="7">
+        <v>315</v>
+      </c>
+      <c r="D18" s="7">
+        <v>320</v>
+      </c>
+      <c r="E18" s="7">
+        <v>325</v>
+      </c>
+      <c r="F18" s="7">
+        <v>330</v>
+      </c>
+      <c r="G18" s="7">
+        <v>335</v>
+      </c>
+      <c r="H18" s="7">
+        <v>335</v>
+      </c>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+      <c r="K18" s="5"/>
       <c r="L18" s="5"/>
       <c r="M18" s="5"/>
       <c r="N18" s="5"/>
@@ -1207,7 +1228,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="C19" s="5"/>
       <c r="D19" s="5"/>
@@ -1234,7 +1255,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
@@ -1261,7 +1282,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C21" s="5"/>
       <c r="D21" s="5"/>
@@ -1284,38 +1305,42 @@
       <c r="O21" s="5"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="2">
+      <c r="A22" s="14">
         <v>20</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
-      <c r="H22" s="5"/>
-      <c r="I22" s="7">
+      <c r="B22" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" s="10"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="10"/>
+      <c r="G22" s="10"/>
+      <c r="H22" s="10"/>
+      <c r="I22" s="10">
         <v>445</v>
       </c>
-      <c r="J22" s="7">
+      <c r="J22" s="10">
         <v>445</v>
       </c>
-      <c r="K22" s="7">
+      <c r="K22" s="10">
         <v>480</v>
       </c>
-      <c r="L22" s="5"/>
-      <c r="M22" s="5"/>
-      <c r="N22" s="5"/>
-      <c r="O22" s="5"/>
+      <c r="L22" s="10">
+        <v>480</v>
+      </c>
+      <c r="M22" s="10">
+        <v>510</v>
+      </c>
+      <c r="N22" s="10"/>
+      <c r="O22" s="10"/>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>21</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="C23" s="5"/>
       <c r="D23" s="5"/>
@@ -1338,38 +1363,38 @@
       <c r="O23" s="5"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A24" s="2">
+      <c r="A24" s="14">
         <v>22</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
-      <c r="H24" s="5"/>
-      <c r="I24" s="7">
+      <c r="B24" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C24" s="10"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="10"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="10"/>
+      <c r="H24" s="10"/>
+      <c r="I24" s="10">
         <v>445</v>
       </c>
-      <c r="J24" s="7">
+      <c r="J24" s="10">
         <v>445</v>
       </c>
-      <c r="K24" s="7">
+      <c r="K24" s="10">
         <v>480</v>
       </c>
-      <c r="L24" s="5"/>
-      <c r="M24" s="5"/>
-      <c r="N24" s="5"/>
-      <c r="O24" s="5"/>
+      <c r="L24" s="10"/>
+      <c r="M24" s="10"/>
+      <c r="N24" s="10"/>
+      <c r="O24" s="10"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>23</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C25" s="5"/>
       <c r="D25" s="5"/>
@@ -1396,7 +1421,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C26" s="5"/>
       <c r="D26" s="5"/>
@@ -1423,7 +1448,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="C27" s="5"/>
       <c r="D27" s="5"/>
@@ -1450,7 +1475,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C28" s="5"/>
       <c r="D28" s="5"/>
@@ -1476,8 +1501,8 @@
       <c r="A29" s="2">
         <v>27</v>
       </c>
-      <c r="B29" s="8" t="s">
-        <v>12</v>
+      <c r="B29" s="6" t="s">
+        <v>18</v>
       </c>
       <c r="C29" s="5"/>
       <c r="D29" s="5"/>
@@ -1485,49 +1510,53 @@
       <c r="F29" s="5"/>
       <c r="G29" s="5"/>
       <c r="H29" s="5"/>
-      <c r="I29" s="5"/>
-      <c r="J29" s="5"/>
-      <c r="K29" s="5"/>
-      <c r="L29" s="7">
-        <v>510</v>
-      </c>
-      <c r="M29" s="7">
-        <v>540</v>
-      </c>
+      <c r="I29" s="7">
+        <v>445</v>
+      </c>
+      <c r="J29" s="7">
+        <v>445</v>
+      </c>
+      <c r="K29" s="7">
+        <v>480</v>
+      </c>
+      <c r="L29" s="5"/>
+      <c r="M29" s="5"/>
       <c r="N29" s="5"/>
       <c r="O29" s="5"/>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A30" s="2">
+      <c r="A30" s="14">
         <v>28</v>
       </c>
-      <c r="B30" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C30" s="5"/>
-      <c r="D30" s="5"/>
-      <c r="E30" s="5"/>
-      <c r="F30" s="5"/>
-      <c r="G30" s="5"/>
-      <c r="H30" s="5"/>
-      <c r="I30" s="5"/>
-      <c r="J30" s="5"/>
-      <c r="K30" s="5"/>
-      <c r="L30" s="7">
-        <v>510</v>
-      </c>
-      <c r="M30" s="7">
-        <v>540</v>
-      </c>
-      <c r="N30" s="5"/>
-      <c r="O30" s="5"/>
+      <c r="B30" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C30" s="10"/>
+      <c r="D30" s="10"/>
+      <c r="E30" s="10"/>
+      <c r="F30" s="10"/>
+      <c r="G30" s="10"/>
+      <c r="H30" s="10"/>
+      <c r="I30" s="10">
+        <v>445</v>
+      </c>
+      <c r="J30" s="10">
+        <v>445</v>
+      </c>
+      <c r="K30" s="10">
+        <v>480</v>
+      </c>
+      <c r="L30" s="10"/>
+      <c r="M30" s="10"/>
+      <c r="N30" s="10"/>
+      <c r="O30" s="10"/>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>29</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C31" s="5"/>
       <c r="D31" s="5"/>
@@ -1535,15 +1564,17 @@
       <c r="F31" s="5"/>
       <c r="G31" s="5"/>
       <c r="H31" s="5"/>
-      <c r="I31" s="5"/>
-      <c r="J31" s="5"/>
-      <c r="K31" s="5"/>
-      <c r="L31" s="7">
-        <v>510</v>
-      </c>
-      <c r="M31" s="7">
-        <v>540</v>
-      </c>
+      <c r="I31" s="7">
+        <v>445</v>
+      </c>
+      <c r="J31" s="7">
+        <v>445</v>
+      </c>
+      <c r="K31" s="7">
+        <v>480</v>
+      </c>
+      <c r="L31" s="5"/>
+      <c r="M31" s="5"/>
       <c r="N31" s="5"/>
       <c r="O31" s="5"/>
     </row>
@@ -1551,8 +1582,8 @@
       <c r="A32" s="2">
         <v>30</v>
       </c>
-      <c r="B32" s="6" t="s">
-        <v>22</v>
+      <c r="B32" s="8" t="s">
+        <v>12</v>
       </c>
       <c r="C32" s="5"/>
       <c r="D32" s="5"/>
@@ -1576,8 +1607,8 @@
       <c r="A33" s="2">
         <v>31</v>
       </c>
-      <c r="B33" s="6" t="s">
-        <v>17</v>
+      <c r="B33" s="8" t="s">
+        <v>29</v>
       </c>
       <c r="C33" s="5"/>
       <c r="D33" s="5"/>
@@ -1588,95 +1619,87 @@
       <c r="I33" s="5"/>
       <c r="J33" s="5"/>
       <c r="K33" s="5"/>
-      <c r="L33" s="5">
+      <c r="L33" s="7">
+        <v>510</v>
+      </c>
+      <c r="M33" s="7">
         <v>540</v>
       </c>
-      <c r="M33" s="5">
-        <v>570</v>
-      </c>
-      <c r="N33" s="5">
-        <v>575</v>
-      </c>
-      <c r="O33" s="5">
-        <v>645</v>
-      </c>
+      <c r="N33" s="5"/>
+      <c r="O33" s="5"/>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A34" s="2">
+      <c r="A34" s="14">
         <v>32</v>
       </c>
-      <c r="B34" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C34" s="5"/>
-      <c r="D34" s="5"/>
-      <c r="E34" s="5"/>
-      <c r="F34" s="5"/>
-      <c r="G34" s="5"/>
-      <c r="H34" s="5"/>
-      <c r="I34" s="5"/>
-      <c r="J34" s="5"/>
-      <c r="K34" s="5"/>
-      <c r="L34" s="5"/>
-      <c r="M34" s="5"/>
-      <c r="N34" s="5">
-        <v>500</v>
-      </c>
-      <c r="O34" s="5">
-        <v>570</v>
-      </c>
+      <c r="B34" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="C34" s="10"/>
+      <c r="D34" s="10"/>
+      <c r="E34" s="10"/>
+      <c r="F34" s="10"/>
+      <c r="G34" s="10"/>
+      <c r="H34" s="10"/>
+      <c r="I34" s="10"/>
+      <c r="J34" s="10"/>
+      <c r="K34" s="10"/>
+      <c r="L34" s="10">
+        <v>510</v>
+      </c>
+      <c r="M34" s="10">
+        <v>540</v>
+      </c>
+      <c r="N34" s="10"/>
+      <c r="O34" s="10"/>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>33</v>
       </c>
-      <c r="B35" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="13"/>
-      <c r="D35" s="13"/>
-      <c r="E35" s="13"/>
-      <c r="F35" s="13"/>
-      <c r="G35" s="13"/>
-      <c r="H35" s="13"/>
-      <c r="I35" s="13"/>
-      <c r="J35" s="13"/>
-      <c r="K35" s="13"/>
-      <c r="L35" s="13"/>
-      <c r="M35" s="13"/>
-      <c r="N35" s="14"/>
-      <c r="O35"/>
+      <c r="B35" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C35" s="5"/>
+      <c r="D35" s="5"/>
+      <c r="E35" s="5"/>
+      <c r="F35" s="5"/>
+      <c r="G35" s="5"/>
+      <c r="H35" s="5"/>
+      <c r="I35" s="5"/>
+      <c r="J35" s="5"/>
+      <c r="K35" s="5"/>
+      <c r="L35" s="7">
+        <v>510</v>
+      </c>
+      <c r="M35" s="7">
+        <v>540</v>
+      </c>
+      <c r="N35" s="5"/>
+      <c r="O35" s="5"/>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>34</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C36" s="7">
-        <v>6.3</v>
-      </c>
-      <c r="D36" s="7">
-        <v>7.2</v>
-      </c>
-      <c r="E36" s="7">
-        <v>8.1999999999999993</v>
-      </c>
-      <c r="F36" s="7">
-        <v>10.8</v>
-      </c>
-      <c r="G36" s="7">
-        <v>12.3</v>
-      </c>
-      <c r="H36" s="7">
-        <v>14.8</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="C36" s="5"/>
+      <c r="D36" s="5"/>
+      <c r="E36" s="5"/>
+      <c r="F36" s="5"/>
+      <c r="G36" s="5"/>
+      <c r="H36" s="5"/>
       <c r="I36" s="5"/>
       <c r="J36" s="5"/>
       <c r="K36" s="5"/>
-      <c r="L36" s="5"/>
-      <c r="M36" s="5"/>
+      <c r="L36" s="7">
+        <v>510</v>
+      </c>
+      <c r="M36" s="7">
+        <v>540</v>
+      </c>
       <c r="N36" s="5"/>
       <c r="O36" s="5"/>
     </row>
@@ -1685,106 +1708,82 @@
         <v>35</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C37" s="7">
-        <v>6.3</v>
-      </c>
-      <c r="D37" s="7">
-        <v>7.2</v>
-      </c>
-      <c r="E37" s="7">
-        <v>8.1999999999999993</v>
-      </c>
-      <c r="F37" s="7">
-        <v>10.8</v>
-      </c>
-      <c r="G37" s="7">
-        <v>12.3</v>
-      </c>
-      <c r="H37" s="7">
-        <v>14.8</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="C37" s="5"/>
+      <c r="D37" s="5"/>
+      <c r="E37" s="5"/>
+      <c r="F37" s="5"/>
+      <c r="G37" s="5"/>
+      <c r="H37" s="5"/>
       <c r="I37" s="5"/>
       <c r="J37" s="5"/>
       <c r="K37" s="5"/>
-      <c r="L37" s="5"/>
-      <c r="M37" s="5"/>
-      <c r="N37" s="5"/>
-      <c r="O37" s="5"/>
+      <c r="L37" s="5">
+        <v>540</v>
+      </c>
+      <c r="M37" s="5">
+        <v>570</v>
+      </c>
+      <c r="N37" s="5">
+        <v>575</v>
+      </c>
+      <c r="O37" s="5">
+        <v>645</v>
+      </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>36</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="7">
-        <v>6.3</v>
-      </c>
-      <c r="D38" s="7">
-        <v>7.2</v>
-      </c>
-      <c r="E38" s="7">
-        <v>8.1999999999999993</v>
-      </c>
-      <c r="F38" s="7">
-        <v>10.8</v>
-      </c>
-      <c r="G38" s="7">
-        <v>12.3</v>
-      </c>
-      <c r="H38" s="7">
-        <v>14.8</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="C38" s="5"/>
+      <c r="D38" s="5"/>
+      <c r="E38" s="5"/>
+      <c r="F38" s="5"/>
+      <c r="G38" s="5"/>
+      <c r="H38" s="5"/>
       <c r="I38" s="5"/>
       <c r="J38" s="5"/>
       <c r="K38" s="5"/>
       <c r="L38" s="5"/>
       <c r="M38" s="5"/>
-      <c r="N38" s="5"/>
-      <c r="O38" s="5"/>
+      <c r="N38" s="5">
+        <v>500</v>
+      </c>
+      <c r="O38" s="5">
+        <v>570</v>
+      </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>37</v>
       </c>
-      <c r="B39" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C39" s="7">
-        <v>6.3</v>
-      </c>
-      <c r="D39" s="7">
-        <v>7.2</v>
-      </c>
-      <c r="E39" s="7">
-        <v>8.1999999999999993</v>
-      </c>
-      <c r="F39" s="7">
-        <v>10.8</v>
-      </c>
-      <c r="G39" s="7">
-        <v>12.3</v>
-      </c>
-      <c r="H39" s="7">
-        <v>14.8</v>
-      </c>
-      <c r="I39" s="5"/>
-      <c r="J39" s="5"/>
-      <c r="K39" s="5"/>
-      <c r="L39" s="5"/>
-      <c r="M39" s="5"/>
-      <c r="N39" s="5"/>
-      <c r="O39" s="5"/>
+      <c r="B39" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="15"/>
+      <c r="D39" s="15"/>
+      <c r="E39" s="15"/>
+      <c r="F39" s="15"/>
+      <c r="G39" s="15"/>
+      <c r="H39" s="15"/>
+      <c r="I39" s="15"/>
+      <c r="J39" s="15"/>
+      <c r="K39" s="15"/>
+      <c r="L39" s="15"/>
+      <c r="M39" s="15"/>
+      <c r="N39" s="15"/>
+      <c r="O39" s="15"/>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>38</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C40" s="7">
         <v>6.3</v>
@@ -1817,7 +1816,7 @@
         <v>39</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="C41" s="7">
         <v>6.3</v>
@@ -1850,7 +1849,7 @@
         <v>40</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C42" s="7">
         <v>6.3</v>
@@ -1883,7 +1882,7 @@
         <v>41</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C43" s="7">
         <v>6.3</v>
@@ -1912,44 +1911,44 @@
       <c r="O43" s="5"/>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A44" s="2">
+      <c r="A44" s="14">
         <v>42</v>
       </c>
-      <c r="B44" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C44" s="7">
+      <c r="B44" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C44" s="10">
         <v>6.3</v>
       </c>
-      <c r="D44" s="7">
+      <c r="D44" s="10">
         <v>7.2</v>
       </c>
-      <c r="E44" s="7">
+      <c r="E44" s="10">
         <v>8.1999999999999993</v>
       </c>
-      <c r="F44" s="7">
+      <c r="F44" s="10">
         <v>10.8</v>
       </c>
-      <c r="G44" s="7">
+      <c r="G44" s="10">
         <v>12.3</v>
       </c>
-      <c r="H44" s="7">
+      <c r="H44" s="10">
         <v>14.8</v>
       </c>
-      <c r="I44" s="5"/>
-      <c r="J44" s="5"/>
-      <c r="K44" s="5"/>
-      <c r="L44" s="5"/>
-      <c r="M44" s="5"/>
-      <c r="N44" s="5"/>
-      <c r="O44" s="5"/>
+      <c r="I44" s="10"/>
+      <c r="J44" s="10"/>
+      <c r="K44" s="10"/>
+      <c r="L44" s="10"/>
+      <c r="M44" s="10"/>
+      <c r="N44" s="10"/>
+      <c r="O44" s="10"/>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>43</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C45" s="7">
         <v>6.3</v>
@@ -1982,7 +1981,7 @@
         <v>44</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C46" s="7">
         <v>6.3</v>
@@ -2015,23 +2014,29 @@
         <v>45</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C47" s="5"/>
-      <c r="D47" s="5"/>
-      <c r="E47" s="5"/>
-      <c r="F47" s="5"/>
-      <c r="G47" s="5"/>
-      <c r="H47" s="5"/>
-      <c r="I47" s="7">
-        <v>19</v>
-      </c>
-      <c r="J47" s="7">
-        <v>23.4</v>
-      </c>
-      <c r="K47" s="7">
-        <v>29.6</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="C47" s="7">
+        <v>6.3</v>
+      </c>
+      <c r="D47" s="7">
+        <v>7.2</v>
+      </c>
+      <c r="E47" s="7">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="F47" s="7">
+        <v>10.8</v>
+      </c>
+      <c r="G47" s="7">
+        <v>12.3</v>
+      </c>
+      <c r="H47" s="7">
+        <v>14.8</v>
+      </c>
+      <c r="I47" s="5"/>
+      <c r="J47" s="5"/>
+      <c r="K47" s="5"/>
       <c r="L47" s="5"/>
       <c r="M47" s="5"/>
       <c r="N47" s="5"/>
@@ -2042,23 +2047,29 @@
         <v>46</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C48" s="5"/>
-      <c r="D48" s="5"/>
-      <c r="E48" s="5"/>
-      <c r="F48" s="5"/>
-      <c r="G48" s="5"/>
-      <c r="H48" s="5"/>
-      <c r="I48" s="7">
-        <v>19</v>
-      </c>
-      <c r="J48" s="7">
-        <v>23.4</v>
-      </c>
-      <c r="K48" s="7">
-        <v>29.6</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="C48" s="7">
+        <v>6.3</v>
+      </c>
+      <c r="D48" s="7">
+        <v>7.2</v>
+      </c>
+      <c r="E48" s="7">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="F48" s="7">
+        <v>10.8</v>
+      </c>
+      <c r="G48" s="7">
+        <v>12.3</v>
+      </c>
+      <c r="H48" s="7">
+        <v>14.8</v>
+      </c>
+      <c r="I48" s="5"/>
+      <c r="J48" s="5"/>
+      <c r="K48" s="5"/>
       <c r="L48" s="5"/>
       <c r="M48" s="5"/>
       <c r="N48" s="5"/>
@@ -2069,77 +2080,95 @@
         <v>47</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C49" s="5"/>
-      <c r="D49" s="5"/>
-      <c r="E49" s="5"/>
-      <c r="F49" s="5"/>
-      <c r="G49" s="5"/>
-      <c r="H49" s="5"/>
-      <c r="I49" s="7">
-        <v>19</v>
-      </c>
-      <c r="J49" s="7">
-        <v>23.4</v>
-      </c>
-      <c r="K49" s="7">
-        <v>29.6</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="C49" s="7">
+        <v>6.3</v>
+      </c>
+      <c r="D49" s="7">
+        <v>7.2</v>
+      </c>
+      <c r="E49" s="7">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="F49" s="7">
+        <v>10.8</v>
+      </c>
+      <c r="G49" s="7">
+        <v>12.3</v>
+      </c>
+      <c r="H49" s="7">
+        <v>14.8</v>
+      </c>
+      <c r="I49" s="5"/>
+      <c r="J49" s="5"/>
+      <c r="K49" s="5"/>
       <c r="L49" s="5"/>
       <c r="M49" s="5"/>
       <c r="N49" s="5"/>
       <c r="O49" s="5"/>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A50" s="2">
+      <c r="A50" s="14">
         <v>48</v>
       </c>
-      <c r="B50" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C50" s="5"/>
-      <c r="D50" s="5"/>
-      <c r="E50" s="5"/>
-      <c r="F50" s="5"/>
-      <c r="G50" s="5"/>
-      <c r="H50" s="5"/>
-      <c r="I50" s="7">
-        <v>19</v>
-      </c>
-      <c r="J50" s="7">
-        <v>23.4</v>
-      </c>
-      <c r="K50" s="7">
-        <v>29.6</v>
-      </c>
-      <c r="L50" s="5"/>
-      <c r="M50" s="5"/>
-      <c r="N50" s="5"/>
-      <c r="O50" s="5"/>
+      <c r="B50" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C50" s="10">
+        <v>6.3</v>
+      </c>
+      <c r="D50" s="10">
+        <v>7.2</v>
+      </c>
+      <c r="E50" s="10">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="F50" s="10">
+        <v>10.8</v>
+      </c>
+      <c r="G50" s="10">
+        <v>12.3</v>
+      </c>
+      <c r="H50" s="10">
+        <v>14.8</v>
+      </c>
+      <c r="I50" s="10"/>
+      <c r="J50" s="10"/>
+      <c r="K50" s="10"/>
+      <c r="L50" s="10"/>
+      <c r="M50" s="10"/>
+      <c r="N50" s="10"/>
+      <c r="O50" s="10"/>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>49</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C51" s="5"/>
-      <c r="D51" s="5"/>
-      <c r="E51" s="5"/>
-      <c r="F51" s="5"/>
-      <c r="G51" s="5"/>
-      <c r="H51" s="5"/>
-      <c r="I51" s="7">
-        <v>19</v>
-      </c>
-      <c r="J51" s="7">
-        <v>23.4</v>
-      </c>
-      <c r="K51" s="7">
-        <v>29.6</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="C51" s="7">
+        <v>6.3</v>
+      </c>
+      <c r="D51" s="7">
+        <v>7.2</v>
+      </c>
+      <c r="E51" s="7">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="F51" s="7">
+        <v>10.8</v>
+      </c>
+      <c r="G51" s="7">
+        <v>12.3</v>
+      </c>
+      <c r="H51" s="7">
+        <v>14.8</v>
+      </c>
+      <c r="I51" s="5"/>
+      <c r="J51" s="5"/>
+      <c r="K51" s="5"/>
       <c r="L51" s="5"/>
       <c r="M51" s="5"/>
       <c r="N51" s="5"/>
@@ -2150,7 +2179,7 @@
         <v>50</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C52" s="5"/>
       <c r="D52" s="5"/>
@@ -2177,7 +2206,7 @@
         <v>51</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="C53" s="5"/>
       <c r="D53" s="5"/>
@@ -2204,7 +2233,7 @@
         <v>52</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="C54" s="5"/>
       <c r="D54" s="5"/>
@@ -2227,38 +2256,42 @@
       <c r="O54" s="5"/>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A55" s="2">
+      <c r="A55" s="14">
         <v>53</v>
       </c>
-      <c r="B55" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C55" s="5"/>
-      <c r="D55" s="5"/>
-      <c r="E55" s="5"/>
-      <c r="F55" s="5"/>
-      <c r="G55" s="5"/>
-      <c r="H55" s="5"/>
-      <c r="I55" s="7">
+      <c r="B55" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C55" s="10"/>
+      <c r="D55" s="10"/>
+      <c r="E55" s="10"/>
+      <c r="F55" s="10"/>
+      <c r="G55" s="10"/>
+      <c r="H55" s="10"/>
+      <c r="I55" s="10">
         <v>19</v>
       </c>
-      <c r="J55" s="7">
+      <c r="J55" s="10">
         <v>23.4</v>
       </c>
-      <c r="K55" s="7">
+      <c r="K55" s="10">
         <v>29.6</v>
       </c>
-      <c r="L55" s="5"/>
-      <c r="M55" s="5"/>
-      <c r="N55" s="5"/>
-      <c r="O55" s="5"/>
+      <c r="L55" s="10">
+        <v>36</v>
+      </c>
+      <c r="M55" s="10">
+        <v>55.8</v>
+      </c>
+      <c r="N55" s="10"/>
+      <c r="O55" s="10"/>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>54</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="C56" s="5"/>
       <c r="D56" s="5"/>
@@ -2281,38 +2314,38 @@
       <c r="O56" s="5"/>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A57" s="2">
+      <c r="A57" s="14">
         <v>55</v>
       </c>
-      <c r="B57" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C57" s="5"/>
-      <c r="D57" s="5"/>
-      <c r="E57" s="5"/>
-      <c r="F57" s="5"/>
-      <c r="G57" s="5"/>
-      <c r="H57" s="5"/>
-      <c r="I57" s="7">
+      <c r="B57" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C57" s="10"/>
+      <c r="D57" s="10"/>
+      <c r="E57" s="10"/>
+      <c r="F57" s="10"/>
+      <c r="G57" s="10"/>
+      <c r="H57" s="10"/>
+      <c r="I57" s="10">
         <v>19</v>
       </c>
-      <c r="J57" s="7">
+      <c r="J57" s="10">
         <v>23.4</v>
       </c>
-      <c r="K57" s="7">
+      <c r="K57" s="10">
         <v>29.6</v>
       </c>
-      <c r="L57" s="5"/>
-      <c r="M57" s="5"/>
-      <c r="N57" s="5"/>
-      <c r="O57" s="5"/>
+      <c r="L57" s="10"/>
+      <c r="M57" s="10"/>
+      <c r="N57" s="10"/>
+      <c r="O57" s="10"/>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>56</v>
       </c>
-      <c r="B58" s="8" t="s">
-        <v>12</v>
+      <c r="B58" s="6" t="s">
+        <v>14</v>
       </c>
       <c r="C58" s="5"/>
       <c r="D58" s="5"/>
@@ -2320,15 +2353,17 @@
       <c r="F58" s="5"/>
       <c r="G58" s="5"/>
       <c r="H58" s="5"/>
-      <c r="I58" s="5"/>
-      <c r="J58" s="5"/>
-      <c r="K58" s="5"/>
-      <c r="L58" s="7">
-        <v>36</v>
-      </c>
-      <c r="M58" s="7">
-        <v>55.8</v>
-      </c>
+      <c r="I58" s="7">
+        <v>19</v>
+      </c>
+      <c r="J58" s="7">
+        <v>23.4</v>
+      </c>
+      <c r="K58" s="7">
+        <v>29.6</v>
+      </c>
+      <c r="L58" s="5"/>
+      <c r="M58" s="5"/>
       <c r="N58" s="5"/>
       <c r="O58" s="5"/>
     </row>
@@ -2336,8 +2371,8 @@
       <c r="A59" s="2">
         <v>57</v>
       </c>
-      <c r="B59" s="8" t="s">
-        <v>31</v>
+      <c r="B59" s="6" t="s">
+        <v>19</v>
       </c>
       <c r="C59" s="5"/>
       <c r="D59" s="5"/>
@@ -2345,15 +2380,17 @@
       <c r="F59" s="5"/>
       <c r="G59" s="5"/>
       <c r="H59" s="5"/>
-      <c r="I59" s="5"/>
-      <c r="J59" s="5"/>
-      <c r="K59" s="5"/>
-      <c r="L59" s="7">
-        <v>36</v>
-      </c>
-      <c r="M59" s="7">
-        <v>55.8</v>
-      </c>
+      <c r="I59" s="7">
+        <v>19</v>
+      </c>
+      <c r="J59" s="7">
+        <v>23.4</v>
+      </c>
+      <c r="K59" s="7">
+        <v>29.6</v>
+      </c>
+      <c r="L59" s="5"/>
+      <c r="M59" s="5"/>
       <c r="N59" s="5"/>
       <c r="O59" s="5"/>
     </row>
@@ -2362,7 +2399,7 @@
         <v>58</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="C60" s="5"/>
       <c r="D60" s="5"/>
@@ -2370,15 +2407,17 @@
       <c r="F60" s="5"/>
       <c r="G60" s="5"/>
       <c r="H60" s="5"/>
-      <c r="I60" s="5"/>
-      <c r="J60" s="5"/>
-      <c r="K60" s="5"/>
-      <c r="L60" s="7">
-        <v>36</v>
-      </c>
-      <c r="M60" s="7">
-        <v>55.8</v>
-      </c>
+      <c r="I60" s="7">
+        <v>19</v>
+      </c>
+      <c r="J60" s="7">
+        <v>23.4</v>
+      </c>
+      <c r="K60" s="7">
+        <v>29.6</v>
+      </c>
+      <c r="L60" s="5"/>
+      <c r="M60" s="5"/>
       <c r="N60" s="5"/>
       <c r="O60" s="5"/>
     </row>
@@ -2387,7 +2426,7 @@
         <v>59</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C61" s="5"/>
       <c r="D61" s="5"/>
@@ -2395,15 +2434,17 @@
       <c r="F61" s="5"/>
       <c r="G61" s="5"/>
       <c r="H61" s="5"/>
-      <c r="I61" s="5"/>
-      <c r="J61" s="5"/>
-      <c r="K61" s="5"/>
-      <c r="L61" s="7">
-        <v>36</v>
-      </c>
-      <c r="M61" s="7">
-        <v>55.8</v>
-      </c>
+      <c r="I61" s="7">
+        <v>19</v>
+      </c>
+      <c r="J61" s="7">
+        <v>23.4</v>
+      </c>
+      <c r="K61" s="7">
+        <v>29.6</v>
+      </c>
+      <c r="L61" s="5"/>
+      <c r="M61" s="5"/>
       <c r="N61" s="5"/>
       <c r="O61" s="5"/>
     </row>
@@ -2412,7 +2453,7 @@
         <v>60</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C62" s="5"/>
       <c r="D62" s="5"/>
@@ -2420,53 +2461,259 @@
       <c r="F62" s="5"/>
       <c r="G62" s="5"/>
       <c r="H62" s="5"/>
-      <c r="I62" s="5"/>
-      <c r="J62" s="5"/>
-      <c r="K62" s="5"/>
-      <c r="L62" s="5">
+      <c r="I62" s="7">
+        <v>19</v>
+      </c>
+      <c r="J62" s="7">
+        <v>23.4</v>
+      </c>
+      <c r="K62" s="7">
+        <v>29.6</v>
+      </c>
+      <c r="L62" s="5"/>
+      <c r="M62" s="5"/>
+      <c r="N62" s="5"/>
+      <c r="O62" s="5"/>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A63" s="14">
+        <v>61</v>
+      </c>
+      <c r="B63" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C63" s="10"/>
+      <c r="D63" s="10"/>
+      <c r="E63" s="10"/>
+      <c r="F63" s="10"/>
+      <c r="G63" s="10"/>
+      <c r="H63" s="10"/>
+      <c r="I63" s="10">
+        <v>19</v>
+      </c>
+      <c r="J63" s="10">
+        <v>23.4</v>
+      </c>
+      <c r="K63" s="10">
+        <v>29.6</v>
+      </c>
+      <c r="L63" s="10"/>
+      <c r="M63" s="10"/>
+      <c r="N63" s="10"/>
+      <c r="O63" s="10"/>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A64" s="2">
+        <v>62</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C64" s="5"/>
+      <c r="D64" s="5"/>
+      <c r="E64" s="5"/>
+      <c r="F64" s="5"/>
+      <c r="G64" s="5"/>
+      <c r="H64" s="5"/>
+      <c r="I64" s="7">
+        <v>19</v>
+      </c>
+      <c r="J64" s="7">
+        <v>23.4</v>
+      </c>
+      <c r="K64" s="7">
+        <v>29.6</v>
+      </c>
+      <c r="L64" s="5"/>
+      <c r="M64" s="5"/>
+      <c r="N64" s="5"/>
+      <c r="O64" s="5"/>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A65" s="2">
+        <v>63</v>
+      </c>
+      <c r="B65" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C65" s="5"/>
+      <c r="D65" s="5"/>
+      <c r="E65" s="5"/>
+      <c r="F65" s="5"/>
+      <c r="G65" s="5"/>
+      <c r="H65" s="5"/>
+      <c r="I65" s="5"/>
+      <c r="J65" s="5"/>
+      <c r="K65" s="5"/>
+      <c r="L65" s="7">
+        <v>36</v>
+      </c>
+      <c r="M65" s="7">
+        <v>55.8</v>
+      </c>
+      <c r="N65" s="5"/>
+      <c r="O65" s="5"/>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A66" s="2">
+        <v>64</v>
+      </c>
+      <c r="B66" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C66" s="5"/>
+      <c r="D66" s="5"/>
+      <c r="E66" s="5"/>
+      <c r="F66" s="5"/>
+      <c r="G66" s="5"/>
+      <c r="H66" s="5"/>
+      <c r="I66" s="5"/>
+      <c r="J66" s="5"/>
+      <c r="K66" s="5"/>
+      <c r="L66" s="7">
+        <v>36</v>
+      </c>
+      <c r="M66" s="7">
+        <v>55.8</v>
+      </c>
+      <c r="N66" s="5"/>
+      <c r="O66" s="5"/>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A67" s="14">
+        <v>65</v>
+      </c>
+      <c r="B67" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="C67" s="10"/>
+      <c r="D67" s="10"/>
+      <c r="E67" s="10"/>
+      <c r="F67" s="10"/>
+      <c r="G67" s="10"/>
+      <c r="H67" s="10"/>
+      <c r="I67" s="10"/>
+      <c r="J67" s="10"/>
+      <c r="K67" s="10"/>
+      <c r="L67" s="10">
+        <v>36</v>
+      </c>
+      <c r="M67" s="10">
+        <v>55.8</v>
+      </c>
+      <c r="N67" s="10"/>
+      <c r="O67" s="10"/>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A68" s="2">
+        <v>66</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C68" s="5"/>
+      <c r="D68" s="5"/>
+      <c r="E68" s="5"/>
+      <c r="F68" s="5"/>
+      <c r="G68" s="5"/>
+      <c r="H68" s="5"/>
+      <c r="I68" s="5"/>
+      <c r="J68" s="5"/>
+      <c r="K68" s="5"/>
+      <c r="L68" s="7">
+        <v>36</v>
+      </c>
+      <c r="M68" s="7">
+        <v>55.8</v>
+      </c>
+      <c r="N68" s="5"/>
+      <c r="O68" s="5"/>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A69" s="2">
+        <v>67</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C69" s="5"/>
+      <c r="D69" s="5"/>
+      <c r="E69" s="5"/>
+      <c r="F69" s="5"/>
+      <c r="G69" s="5"/>
+      <c r="H69" s="5"/>
+      <c r="I69" s="5"/>
+      <c r="J69" s="5"/>
+      <c r="K69" s="5"/>
+      <c r="L69" s="7">
+        <v>36</v>
+      </c>
+      <c r="M69" s="7">
+        <v>55.8</v>
+      </c>
+      <c r="N69" s="5"/>
+      <c r="O69" s="5"/>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A70" s="2">
+        <v>68</v>
+      </c>
+      <c r="B70" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C70" s="5"/>
+      <c r="D70" s="5"/>
+      <c r="E70" s="5"/>
+      <c r="F70" s="5"/>
+      <c r="G70" s="5"/>
+      <c r="H70" s="5"/>
+      <c r="I70" s="5"/>
+      <c r="J70" s="5"/>
+      <c r="K70" s="5"/>
+      <c r="L70" s="5">
         <v>37</v>
       </c>
-      <c r="M62" s="5">
+      <c r="M70" s="5">
         <v>56.8</v>
       </c>
-      <c r="N62" s="5">
+      <c r="N70" s="5">
         <v>68</v>
       </c>
-      <c r="O62" s="5">
+      <c r="O70" s="5">
         <v>78</v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A63" s="2">
-        <v>61</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C63" s="5"/>
-      <c r="D63" s="5"/>
-      <c r="E63" s="5"/>
-      <c r="F63" s="5"/>
-      <c r="G63" s="5"/>
-      <c r="H63" s="5"/>
-      <c r="I63" s="5"/>
-      <c r="J63" s="5"/>
-      <c r="K63" s="5"/>
-      <c r="L63" s="5"/>
-      <c r="M63" s="5"/>
-      <c r="N63" s="5">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A71" s="2">
+        <v>69</v>
+      </c>
+      <c r="B71" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C71" s="5"/>
+      <c r="D71" s="5"/>
+      <c r="E71" s="5"/>
+      <c r="F71" s="5"/>
+      <c r="G71" s="5"/>
+      <c r="H71" s="5"/>
+      <c r="I71" s="5"/>
+      <c r="J71" s="5"/>
+      <c r="K71" s="5"/>
+      <c r="L71" s="5"/>
+      <c r="M71" s="5"/>
+      <c r="N71" s="5">
         <v>68</v>
       </c>
-      <c r="O63" s="5">
+      <c r="O71" s="5">
         <v>78</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="B35:N35"/>
-    <mergeCell ref="B6:N6"/>
+    <mergeCell ref="B6:O6"/>
     <mergeCell ref="C2:O2"/>
+    <mergeCell ref="B39:O39"/>
+    <mergeCell ref="A1:O1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/TeplosilaWeb/Content/properties/gtrv3.xlsx
+++ b/TeplosilaWeb/Content/properties/gtrv3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pge27\OneDrive\Рабочий стол\TeploSilaWeb\TeplosilaWeb\Content\properties\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F5C12746-E548-47BA-B237-614272E24B09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93EC2E37-E94F-40CE-A29D-48096687A476}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-5025" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -112,15 +112,6 @@
     <t>TSL-2200-40-2AR-24-IP67</t>
   </si>
   <si>
-    <t>TSL-1600-25-2-24-IP67</t>
-  </si>
-  <si>
-    <t>TSL-2200-40-2-24-IP67</t>
-  </si>
-  <si>
-    <t>TSL-3000-60-2-24-IP67</t>
-  </si>
-  <si>
     <t>TRV-3</t>
   </si>
   <si>
@@ -155,6 +146,15 @@
   </si>
   <si>
     <t>TSL-3000-60-2T-230-IP67</t>
+  </si>
+  <si>
+    <t>TSL-1600-25-2М-24-IP67</t>
+  </si>
+  <si>
+    <t>TSL-2200-40-2М-24-IP67</t>
+  </si>
+  <si>
+    <t>TSL-3000-60-2М-24-IP67</t>
   </si>
 </sst>
 </file>
@@ -625,7 +625,7 @@
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
@@ -709,7 +709,7 @@
         <v>200</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
@@ -865,7 +865,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C8" s="7">
         <v>315</v>
@@ -931,7 +931,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="C10" s="7">
         <v>315</v>
@@ -964,7 +964,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C11" s="10">
         <v>315</v>
@@ -1063,7 +1063,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C14" s="7">
         <v>315</v>
@@ -1162,7 +1162,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C17" s="10">
         <v>315</v>
@@ -1255,7 +1255,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
@@ -1309,7 +1309,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C22" s="10"/>
       <c r="D22" s="10"/>
@@ -1340,7 +1340,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="C23" s="5"/>
       <c r="D23" s="5"/>
@@ -1367,7 +1367,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C24" s="10"/>
       <c r="D24" s="10"/>
@@ -1448,7 +1448,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C27" s="5"/>
       <c r="D27" s="5"/>
@@ -1529,7 +1529,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C30" s="10"/>
       <c r="D30" s="10"/>
@@ -1608,7 +1608,7 @@
         <v>31</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="C33" s="5"/>
       <c r="D33" s="5"/>
@@ -1633,7 +1633,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C34" s="10"/>
       <c r="D34" s="10"/>
@@ -1816,7 +1816,7 @@
         <v>39</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C41" s="7">
         <v>6.3</v>
@@ -1882,7 +1882,7 @@
         <v>41</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="C43" s="7">
         <v>6.3</v>
@@ -1915,7 +1915,7 @@
         <v>42</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C44" s="10">
         <v>6.3</v>
@@ -2014,7 +2014,7 @@
         <v>45</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C47" s="7">
         <v>6.3</v>
@@ -2113,7 +2113,7 @@
         <v>48</v>
       </c>
       <c r="B50" s="13" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C50" s="10">
         <v>6.3</v>
@@ -2206,7 +2206,7 @@
         <v>51</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C53" s="5"/>
       <c r="D53" s="5"/>
@@ -2260,7 +2260,7 @@
         <v>53</v>
       </c>
       <c r="B55" s="13" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="10"/>
@@ -2291,7 +2291,7 @@
         <v>54</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="C56" s="5"/>
       <c r="D56" s="5"/>
@@ -2318,7 +2318,7 @@
         <v>55</v>
       </c>
       <c r="B57" s="13" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="10"/>
@@ -2399,7 +2399,7 @@
         <v>58</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C60" s="5"/>
       <c r="D60" s="5"/>
@@ -2480,7 +2480,7 @@
         <v>61</v>
       </c>
       <c r="B63" s="13" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="10"/>
@@ -2559,7 +2559,7 @@
         <v>64</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="C66" s="5"/>
       <c r="D66" s="5"/>
@@ -2584,7 +2584,7 @@
         <v>65</v>
       </c>
       <c r="B67" s="13" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="10"/>
